--- a/stories/arbres/TREE-LAN-011.xlsx
+++ b/stories/arbres/TREE-LAN-011.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nora est à la cuisine avec papa. Sur la table : une poire, une chaussette, une cuillère. Papa dit : on nomme. On classe. C'est une catégorie. Fruits ensemble. Habits ensemble.</t>
+          <t>Nora est à la cuisine avec papa. Sur la table : une poire, une chaussette, une cuillère. On nomme. On classe. C'est une catégorie. Fruits ensemble. Habits ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est à la cuisine avec papa. Sur la table : une poire, une chaussette, une cuillère.
+papa|On nomme. On classe. C'est une catégorie. Fruits ensemble. Habits ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la table, le tiroir, ou le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, Nora classe. Une catégorie pour les fruits. Une pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, que fait Nora ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a classé. C'est une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les fruits, les habits, ou les couverts.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora met les fruits dans un bol. Catégorie des fruits.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les fruits, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les fruits, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les fruits, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora plie le bonnet. Catégorie des habits.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les habits, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les habits, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les habits, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose les couverts. Catégorie des couverts.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les couverts, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les couverts, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les couverts, c'est une catégorie, à la table. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6469,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Au tiroir, Nora classe. Catégorie des couverts. Elle nomme.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6650,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Au tiroir, que fait Nora ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6823,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On nomme. On classe. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7014,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les fruits, les habits, ou les couverts.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7181,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Au tiroir, les fruits ? Non. Nora classe les couverts. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7372,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7539,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les fruits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7706,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7873,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les fruits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8040,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8207,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les fruits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8374,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8541,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Les habits au tiroir. Nora classe. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8732,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8899,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les habits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9066,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9233,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les habits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9400,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9567,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les habits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9734,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9901,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Les couverts glissent. Nora nomme. Elle classe. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10092,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10259,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les couverts, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10426,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10593,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les couverts, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10760,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10927,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les couverts, c'est une catégorie, à le tiroir. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11094,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11261,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le panier, Nora classe. C'est une catégorie. Fruits ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11442,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le panier, que fait Nora ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11615,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Nora met ensemble. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11806,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les fruits, les habits, ou les couverts.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11973,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le panier, les fruits. Nora classe. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12164,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12331,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les fruits, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12498,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12665,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les fruits, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12832,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +12999,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les fruits, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13166,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13333,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Les habits dans le panier. Nora classe. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13524,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13691,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les habits, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les habits, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14192,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14359,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les habits, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14526,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14693,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Une cuillère au panier. Nora classe. Catégorie des couverts.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14884,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15051,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la poire. les couverts, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15218,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15385,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre le bonnet. les couverts, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15552,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15719,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nora montre la cuillère. les couverts, c'est une catégorie, à le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15886,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15926,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-LAN-011.xlsx
+++ b/stories/arbres/TREE-LAN-011.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|On nomme. On classe. C'est une catégorie. Fruits ensemble. Habits ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre la table, le tiroir, ou le panier.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|À la table, Nora classe. Une catégorie pour les fruits. Une pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|À la table, que fait Nora ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Nora a classé. C'est une catégorie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les fruits, les habits, ou les couverts.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Nora met les fruits dans un bol. Catégorie des fruits.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Nora montre la poire. les fruits, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Nora montre le bonnet. les fruits, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Nora montre la cuillère. les fruits, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Nora plie le bonnet. Catégorie des habits.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Nora montre la poire. les habits, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Nora montre le bonnet. les habits, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Nora montre la cuillère. les habits, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Nora pose les couverts. Catégorie des couverts.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Nora montre la poire. les couverts, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Nora montre le bonnet. les couverts, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Nora montre la cuillère. les couverts, c'est une catégorie, à la table. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6474,6 +6509,7 @@
           <t>narrateur|Au tiroir, Nora classe. Catégorie des couverts. Elle nomme.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6657,6 +6693,7 @@
           <t>narrateur|Au tiroir, que fait Nora ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6828,6 +6865,7 @@
           <t>narrateur|Oui. On nomme. On classe. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7019,6 +7057,7 @@
           <t>narrateur|On peut prendre les fruits, les habits, ou les couverts.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7186,6 +7225,7 @@
           <t>narrateur|Au tiroir, les fruits ? Non. Nora classe les couverts. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7377,6 +7417,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7544,6 +7585,7 @@
           <t>narrateur|Nora montre la poire. les fruits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7711,6 +7753,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7878,6 +7921,7 @@
           <t>narrateur|Nora montre le bonnet. les fruits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8045,6 +8089,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8212,6 +8257,7 @@
           <t>narrateur|Nora montre la cuillère. les fruits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8379,6 +8425,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8546,6 +8593,7 @@
           <t>narrateur|Les habits au tiroir. Nora classe. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8737,6 +8785,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8904,6 +8953,7 @@
           <t>narrateur|Nora montre la poire. les habits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9071,6 +9121,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9238,6 +9289,7 @@
           <t>narrateur|Nora montre le bonnet. les habits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9405,6 +9457,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9572,6 +9625,7 @@
           <t>narrateur|Nora montre la cuillère. les habits, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9739,6 +9793,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9906,6 +9961,7 @@
           <t>narrateur|Les couverts glissent. Nora nomme. Elle classe. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10097,6 +10153,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10264,6 +10321,7 @@
           <t>narrateur|Nora montre la poire. les couverts, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10431,6 +10489,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10598,6 +10657,7 @@
           <t>narrateur|Nora montre le bonnet. les couverts, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10765,6 +10825,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10932,6 +10993,7 @@
           <t>narrateur|Nora montre la cuillère. les couverts, c'est une catégorie, à le tiroir. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11099,6 +11161,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11266,6 +11329,7 @@
           <t>narrateur|Dans le panier, Nora classe. C'est une catégorie. Fruits ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11449,6 +11513,7 @@
           <t>narrateur|Dans le panier, que fait Nora ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11620,6 +11685,7 @@
           <t>narrateur|Nora met ensemble. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11811,6 +11877,7 @@
           <t>narrateur|On peut prendre les fruits, les habits, ou les couverts.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11978,6 +12045,7 @@
           <t>narrateur|Dans le panier, les fruits. Nora classe. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12169,6 +12237,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12336,6 +12405,7 @@
           <t>narrateur|Nora montre la poire. les fruits, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12503,6 +12573,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12670,6 +12741,7 @@
           <t>narrateur|Nora montre le bonnet. les fruits, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12837,6 +12909,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13004,6 +13077,7 @@
           <t>narrateur|Nora montre la cuillère. les fruits, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13171,6 +13245,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13338,6 +13413,7 @@
           <t>narrateur|Les habits dans le panier. Nora classe. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13529,6 +13605,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13696,6 +13773,7 @@
           <t>narrateur|Nora montre la poire. les habits, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13863,6 +13941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14030,6 +14109,7 @@
           <t>narrateur|Nora montre le bonnet. les habits, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14197,6 +14277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14364,6 +14445,7 @@
           <t>narrateur|Nora montre la cuillère. les habits, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14531,6 +14613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14698,6 +14781,7 @@
           <t>narrateur|Une cuillère au panier. Nora classe. Catégorie des couverts.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14889,6 +14973,7 @@
           <t>narrateur|On peut prendre la poire, le bonnet, ou la cuillère.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15056,6 +15141,7 @@
           <t>narrateur|Nora montre la poire. les couverts, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15223,6 +15309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15390,6 +15477,7 @@
           <t>narrateur|Nora montre le bonnet. les couverts, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15557,6 +15645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15724,6 +15813,7 @@
           <t>narrateur|Nora montre la cuillère. les couverts, c'est une catégorie, à le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15891,6 +15981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15909,7 +16000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15933,6 +16024,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15947,7 +16052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16134,6 +16239,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
